--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_286_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_286_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>2</v>
@@ -1531,16 +1531,16 @@
         <v>22</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>7</v>
@@ -3295,16 +3295,16 @@
         <v>15</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>114</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>23</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>2</v>
@@ -5272,7 +5272,7 @@
         <v>8</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>2</v>
@@ -6448,7 +6448,7 @@
         <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>91</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_286_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_286_EL.xlsx
@@ -614,11 +614,26 @@
           <t>Gen/TO</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr"/>
+      <c r="AM1" s="1" t="inlineStr"/>
+      <c r="AN1" s="1" t="inlineStr"/>
+      <c r="AO1" s="1" t="inlineStr"/>
+      <c r="AP1" s="1" t="inlineStr"/>
+      <c r="AQ1" s="1" t="inlineStr"/>
+      <c r="AR1" s="1" t="inlineStr"/>
+      <c r="AS1" s="1" t="inlineStr"/>
+      <c r="AT1" s="1" t="inlineStr"/>
+      <c r="AU1" s="1" t="inlineStr"/>
+      <c r="AV1" s="1" t="inlineStr"/>
+      <c r="AW1" s="1" t="inlineStr"/>
+      <c r="AX1" s="1" t="inlineStr"/>
+      <c r="AY1" s="1" t="inlineStr"/>
+      <c r="AZ1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CRVENA ZVEZDA MERIDIAN BELGRADE</t>
+          <t>CRVENA ZVEZDA MERIDIANBET BELGRADE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,6 +788,21 @@
           <t>9.44</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -932,6 +962,183 @@
           <t>11.29</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,6 +1151,56 @@
           <t>CORTES, CARLOS (Spain)</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -956,6 +1213,56 @@
           <t>ALIAGA, JORDI (Spain)</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -968,6 +1275,56 @@
           <t>THEPENIER, HUGUES (France)</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -980,6 +1337,56 @@
           <t>-</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -992,6 +1399,56 @@
           <t>-</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1004,271 +1461,480 @@
           <t>-</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRVENA ZVEZDA MERIDIAN BELGRADE</t>
-        </is>
-      </c>
+          <t>CRVENA ZVEZDA MERIDIANBET BELGRADE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>JUGADOR</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2PM</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2PA</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>3PM</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>3PA</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>FTM</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>FTA</t>
         </is>
       </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>DRB</t>
         </is>
       </c>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>ORB</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>BLK</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>BLK A.</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="Q16" s="1" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="R16" s="1" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>EFI</t>
         </is>
       </c>
-      <c r="T16" s="1" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="U16" s="1" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="V16" s="1" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>FastB Opp</t>
         </is>
       </c>
-      <c r="X16" s="1" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="Y16" s="1" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="Z16" s="1" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AA16" s="1" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="AB16" s="1" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="AC16" s="1" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AD16" s="1" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="AE16" s="1" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="AF16" s="1" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AG16" s="1" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="AH16" s="1" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="AI16" s="1" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AJ16" s="1" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AK16" s="1" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AL16" s="1" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AM16" s="1" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="AN16" s="1" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>PLAYS</t>
         </is>
       </c>
-      <c r="AO16" s="1" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="AP16" s="1" t="inlineStr">
+      <c r="AP16" t="inlineStr">
         <is>
           <t>TS%</t>
         </is>
       </c>
-      <c r="AQ16" s="1" t="inlineStr">
+      <c r="AQ16" t="inlineStr">
         <is>
           <t>PTS/PLAY</t>
         </is>
       </c>
-      <c r="AR16" s="1" t="inlineStr">
+      <c r="AR16" t="inlineStr">
         <is>
           <t>TO%</t>
         </is>
       </c>
-      <c r="AS16" s="1" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="AT16" s="1" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AU16" s="1" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>Sh/TO</t>
         </is>
       </c>
-      <c r="AV16" s="1" t="inlineStr">
+      <c r="AV16" t="inlineStr">
         <is>
           <t>Gen/TO</t>
         </is>
       </c>
-      <c r="AW16" s="1" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>USG%</t>
         </is>
       </c>
-      <c r="AX16" s="1" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>OR%</t>
         </is>
       </c>
-      <c r="AY16" s="1" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>DR%</t>
         </is>
       </c>
-      <c r="AZ16" s="1" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>pAST%</t>
         </is>
@@ -3962,270 +4628,429 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+    </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>ANADOLU EFES ISTANBUL</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>JUGADOR</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>2PM</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2PA</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>3PM</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>3PA</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>FTM</t>
         </is>
       </c>
-      <c r="H34" s="1" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>FTA</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>DRB</t>
         </is>
       </c>
-      <c r="K34" s="1" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>ORB</t>
         </is>
       </c>
-      <c r="L34" s="1" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="M34" s="1" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>BLK</t>
         </is>
       </c>
-      <c r="N34" s="1" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>BLK A.</t>
         </is>
       </c>
-      <c r="O34" s="1" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="P34" s="1" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="Q34" s="1" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="R34" s="1" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="S34" s="1" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>EFI</t>
         </is>
       </c>
-      <c r="T34" s="1" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="U34" s="1" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="V34" s="1" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="W34" s="1" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>FastB Opp</t>
         </is>
       </c>
-      <c r="X34" s="1" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="Y34" s="1" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="Z34" s="1" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AA34" s="1" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="AB34" s="1" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="AC34" s="1" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AD34" s="1" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="AE34" s="1" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="AF34" s="1" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AG34" s="1" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="AH34" s="1" t="inlineStr">
+      <c r="AH34" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="AI34" s="1" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AJ34" s="1" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AK34" s="1" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AL34" s="1" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AM34" s="1" t="inlineStr">
+      <c r="AM34" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="AN34" s="1" t="inlineStr">
+      <c r="AN34" t="inlineStr">
         <is>
           <t>PLAYS</t>
         </is>
       </c>
-      <c r="AO34" s="1" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="AP34" s="1" t="inlineStr">
+      <c r="AP34" t="inlineStr">
         <is>
           <t>TS%</t>
         </is>
       </c>
-      <c r="AQ34" s="1" t="inlineStr">
+      <c r="AQ34" t="inlineStr">
         <is>
           <t>PTS/PLAY</t>
         </is>
       </c>
-      <c r="AR34" s="1" t="inlineStr">
+      <c r="AR34" t="inlineStr">
         <is>
           <t>TO%</t>
         </is>
       </c>
-      <c r="AS34" s="1" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="AT34" s="1" t="inlineStr">
+      <c r="AT34" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AU34" s="1" t="inlineStr">
+      <c r="AU34" t="inlineStr">
         <is>
           <t>Sh/TO</t>
         </is>
       </c>
-      <c r="AV34" s="1" t="inlineStr">
+      <c r="AV34" t="inlineStr">
         <is>
           <t>Gen/TO</t>
         </is>
       </c>
-      <c r="AW34" s="1" t="inlineStr">
+      <c r="AW34" t="inlineStr">
         <is>
           <t>USG%</t>
         </is>
       </c>
-      <c r="AX34" s="1" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>OR%</t>
         </is>
       </c>
-      <c r="AY34" s="1" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>DR%</t>
         </is>
       </c>
-      <c r="AZ34" s="1" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>pAST%</t>
         </is>
@@ -6919,24 +7744,341 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>--- Glossary of Terms ---</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6949,6 +8091,56 @@
           <t>Efficiency Rating (Official ACB/FEB Formula): (PTS + REB + AST + STL + BLK + F+) - (FGA-FGM + FTA-FTM + TO + BLK A. + F)</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6961,6 +8153,56 @@
           <t>Blocks Against: A player's shot attempt was blocked by an opponent.</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6973,6 +8215,56 @@
           <t>Fouls Received: The number of times a player was fouled by an opponent.</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6985,6 +8277,56 @@
           <t>Unforced Turnovers: Turnovers not resulting from a direct steal (e.g., bad pass, out of bounds).</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6997,6 +8339,56 @@
           <t>2nd Chance Points: Points scored within 8 seconds immediately following an offensive rebound.</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7009,6 +8401,56 @@
           <t>Points off Turnovers: Points scored on any possession that was initiated by an opponent's turnover (possession-based).</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7021,6 +8463,56 @@
           <t>Fast Break Points: Points scored by a player on a fast break. Includes points from FTs after a foul.</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7033,6 +8525,56 @@
           <t>Fast Break Opportunity: When a player scores a FG or is fouled on a fast break. A fast break is a play within 8 seconds of a DRB, STL, or opponent's made basket.</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7045,6 +8587,56 @@
           <t>An estimate of possessions used by a player. Formula: FGA + (0.44 * FTA) + TO</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7057,6 +8649,56 @@
           <t>Effective Field Goal Percentage. Adjusts for the fact that a 3-point field goal is worth more than a 2-point field goal.</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7069,6 +8711,56 @@
           <t>True Shooting Percentage. Measures shooting efficiency, taking into account 2-pt, 3-pt, and free throws.</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7081,6 +8773,56 @@
           <t>Turnover Percentage. An estimate of turnovers per 100 plays.</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7093,6 +8835,56 @@
           <t>Free Throw Rate. How frequently a player scores from the free throw line relative to their field goal attempts.</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7105,6 +8897,56 @@
           <t>Assist to Turnover Ratio. A measure of a player's ball security and playmaking.</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7117,6 +8959,56 @@
           <t>Shot to Turnover Ratio. The number of field goal attempts a player takes for every turnover they commit.</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7129,6 +9021,56 @@
           <t>Generated Offense to Turnover Ratio. The number of shots and assists a player generates for every turnover.</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7141,6 +9083,56 @@
           <t>Usage Rate. An estimate of the percentage of a team's offensive possessions a player 'uses' while on the floor.</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7153,6 +9145,56 @@
           <t>Offensive/Defensive Rebound Percentage. Percentage of available offensive/defensive rebounds a player secured while on the floor.</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7165,6 +9207,56 @@
           <t>Assist Percentage. An estimate of the percentage of teammate field goals a player assisted on while on the floor.</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_286_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_286_EL.xlsx
@@ -689,10 +689,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -863,10 +863,10 @@
         <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -884,17 +884,17 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V3" t="n">
         <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -2601,14 +2601,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3189,14 +3189,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -3385,14 +3385,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3581,14 +3581,14 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3973,14 +3973,14 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -4505,14 +4505,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -5325,14 +5325,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" t="n">
         <v>3</v>
       </c>
-      <c r="Y36" t="n">
-        <v>4</v>
-      </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -5361,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -5372,11 +5372,11 @@
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -5521,10 +5521,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5717,14 +5717,14 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -6305,14 +6305,14 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6501,14 +6501,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -7621,14 +7621,14 @@
         <v>6</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -7657,22 +7657,22 @@
         <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>8</v>
       </c>
       <c r="AK48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
